--- a/questionnaire_data/truth_or_thought_research_data.xlsx
+++ b/questionnaire_data/truth_or_thought_research_data.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Pre_Questionnaire" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Post_Questionnaire" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Exit_Questionnaire" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Research_Pre_Questionnaire" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -837,7 +838,6 @@
       <c r="R4" t="n">
         <v>3</v>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -948,4 +948,92 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Session_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>User_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Task_Preference</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bias_Detection_Task_Difference</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Personnel_Influence_Rating</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Overall_Tool_Value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Research_Feedback</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>session_1755522322104_v4sj0tduq</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025-08-18T13:05:22.104Z</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/questionnaire_data/truth_or_thought_research_data.xlsx
+++ b/questionnaire_data/truth_or_thought_research_data.xlsx
@@ -956,7 +956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1027,11 +1027,45 @@
           <t>session</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>session_1755975559810_jz6rwsdrv</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-08-23T18:59:19.810Z</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>session_1755976080004_40o3ksnv0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-08-23T19:08:00.004Z</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/questionnaire_data/truth_or_thought_research_data.xlsx
+++ b/questionnaire_data/truth_or_thought_research_data.xlsx
@@ -956,7 +956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1061,11 +1061,28 @@
           <t>session</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>session_1756053551253_n1bgiu0gi</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-08-24T16:39:11.253Z</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/questionnaire_data/truth_or_thought_research_data.xlsx
+++ b/questionnaire_data/truth_or_thought_research_data.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Post_Questionnaire" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Exit_Questionnaire" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Research_Pre_Questionnaire" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Bias_Analysis_Post_Part2_Questionnaire" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,10 +544,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
@@ -560,7 +561,7 @@
     <col width="27" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="37" customWidth="1" min="15" max="15"/>
+    <col width="48" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
     <col width="6" customWidth="1" min="17" max="17"/>
     <col width="6" customWidth="1" min="18" max="18"/>
@@ -837,6 +838,75 @@
       </c>
       <c r="R4" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>session_1756057059381_y5fnfidak</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-08-24T17:55:10.766Z</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>citationsSources, impactfulQuotes, sourceLabel</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -850,10 +920,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
@@ -945,6 +1015,31 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>exit_1756058790136_7dkhchg4r</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-08-24T18:06:30.136Z</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Summarization of the article would be a good feature to have in Task 2. I helps me quickly get up to speed, otherwise there is a lot of content to read in traditional news outlets which becomes mentally draining.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -956,7 +1051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1078,11 +1173,194 @@
           <t>session</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>session_1756057059381_y5fnfidak</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-08-24T17:37:39.382Z</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>session_1756058871644_fyz9njhsx</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-08-24T18:07:51.644Z</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>session_1756058960105_q7ca1g0v9</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-08-24T18:09:20.105Z</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>session_1756059062473_hkw4pctmg</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-08-24T18:11:02.473Z</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>session_1756060582273_f80bglidx</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-08-24T18:36:22.273Z</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>dasda</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Session_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>User_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Task_Preference</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bias_Detection_Task_Difference</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Personnel_Influence_Rating</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Overall_Tool_Value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Research_Feedback</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>b46f74a4-ef8d-4af2-b870-ae4ee56feebe</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025-08-24T21:49:14.719Z</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>b46f74a4-ef8d-4af2-b870-ae4ee56feebe</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/questionnaire_data/truth_or_thought_research_data.xlsx
+++ b/questionnaire_data/truth_or_thought_research_data.xlsx
@@ -920,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1040,6 +1040,34 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>exit_1756136902439_y582cefg</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-08-25T15:48:22.439Z</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>exit</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1051,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1271,6 +1299,74 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>dasda</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>session_1756135869711_br0xt3v1l</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-08-25T15:31:09.711Z</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>session_1756136083415_55ikx6xrr</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-08-25T15:34:43.415Z</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>session_1756136313290_pypu2set1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-08-25T15:38:33.290Z</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>session_1756136428583_r12618prk</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-08-25T15:40:28.583Z</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>session</t>
         </is>
       </c>
     </row>
@@ -1356,11 +1452,6 @@
           <t>b46f74a4-ef8d-4af2-b870-ae4ee56feebe</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/questionnaire_data/truth_or_thought_research_data.xlsx
+++ b/questionnaire_data/truth_or_thought_research_data.xlsx
@@ -1056,12 +1056,9 @@
           <t>exit</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>no</t>
@@ -1079,7 +1076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1367,6 +1364,32 @@
       <c r="C14" t="inlineStr">
         <is>
           <t>session</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>session_1756149833206_q23asgx6z</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-08-25T19:23:53.206Z</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>

--- a/questionnaire_data/truth_or_thought_research_data.xlsx
+++ b/questionnaire_data/truth_or_thought_research_data.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Exit_Questionnaire" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Research_Pre_Questionnaire" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Bias_Analysis_Post_Part2_Questionnaire" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Bias_Analysis_Questionnaire" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -544,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -906,6 +907,69 @@
         <v>4</v>
       </c>
       <c r="S5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>session_1755944984223_g1z86z93r</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-08-25T20:55:58.445Z</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>citationsSources, impactfulQuotes</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1383,10 +1447,6 @@
           <t>session</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>no</t>
@@ -1479,4 +1539,118 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Session_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>User_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Task_Preference</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bias_Detection_Task_Difference</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Personnel_Influence_Rating</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Overall_Tool_Value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Research_Feedback</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8d9c83d2-0a0d-42c0-8038-bda1b8464a52</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025-08-25T21:09:48.021Z</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8d9c83d2-0a0d-42c0-8038-bda1b8464a52</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>illa</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>8d9c83d2-0a0d-42c0-8038-bda1b8464a52</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-08-25T21:32:50.138Z</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8d9c83d2-0a0d-42c0-8038-bda1b8464a52</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>hogalo</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/questionnaire_data/truth_or_thought_research_data.xlsx
+++ b/questionnaire_data/truth_or_thought_research_data.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Research_Pre_Questionnaire" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Bias_Analysis_Post_Part2_Questionnaire" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Bias_Analysis_Questionnaire" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Research_Post_Questionnaire" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -545,12 +546,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
@@ -971,6 +972,132 @@
       </c>
       <c r="S6" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>8670837b-1964-4701-b4e0-e5f1f67f6dfa</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-08-25T21:42:33.129Z</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8670837b-1964-4701-b4e0-e5f1f67f6dfa</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>citationsSources, sourceLabel</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>session_1755944984223_g1z86z93r</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-08-26T01:28:30.218Z</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>impactfulQuotes, sourceLabel, citationsSources</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1547,7 +1674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1640,13 +1767,135 @@
           <t>8d9c83d2-0a0d-42c0-8038-bda1b8464a52</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>hogalo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>test_column_alignment_bias</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-08-26T01:43:00.000Z</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>great tool</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Session_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>User_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Task_Preference</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bias_Detection_Task_Difference</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Personnel_Influence_Rating</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Overall_Tool_Value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Research_Feedback</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>api_test_session_1000000000</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025-08-25T21:44:00.000Z</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>test_column_alignment_post</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-08-26T01:43:00.000Z</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>test</t>
         </is>
       </c>
     </row>
